--- a/docs/enhanced_qa_pairs.xlsx
+++ b/docs/enhanced_qa_pairs.xlsx
@@ -46,301 +46,58 @@
     <t>사업연결은 어떻게해?</t>
   </si>
   <si>
-    <t>[
-  "비밀번호를 분실했을 경우 어떻게 해야 할까요?",
-  "혹시 비밀번호를 잊어버렸다면 어떤 방법으로 찾을 수 있을까요?",
-  "로그인 비밀번호를 기억나지 않을 때는 어떻게 해야 하나요?"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "연장 근무 수당은 어떤 경우에 발생하나요?",
-  "연장 수당이 지급되는 조건은 무엇인가요?",
-  "어떤 경우에 연장 근무에 대한 수당을 받을 수 있나요?"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "주휴수당이 발생하는 조건은 무엇인가요?",
-  "주휴수당 지급에 관한 자세한 조건을 알고 싶습니다.",
-  "어떤 경우에 주휴수당을 받을 수 있나요?"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "휴일 근무에 대한 수당은 어떻게 지급되나요?",
-  "휴일 근무 시 추가로 받을 수 있는 수당은 무엇인가요?",
-  "공휴일에 일했을 때 받는 수당에 대해 알고 싶습니다."
-]</t>
-  </si>
-  <si>
-    <t>[
-  "노무비 명세서 작성 방법을 알려주시겠습니까?",
-  "노무비 명세서를 어떻게 작성해야 하는지 자세히 설명해주세요.",
-  "노무비 명세서 작성에 대해 안내 부탁드립니다."
-]</t>
-  </si>
-  <si>
-    <t>[
-  "사업 연결 방법을 알려주시겠습니까?",
-  "어떻게 하면 사업을 연결할 수 있을까요?",
-  "사업 연결 절차에 대해 자세히 설명해 주시겠습니까?"
-]</t>
-  </si>
-  <si>
-    <t>{
-  "basic_rules": [
-    "로그인 화면에서 비밀번호 찾기 기능을 이용하시면 됩니다.",
-    "본인 확인 절차를 거쳐야 비밀번호를 재설정하실 수 있습니다."
-  ],
-  "examples": [
-    {
-      "scenario": "회원님께서 비밀번호를 잊어버리셨고, 휴대폰 번호가 등록되어 있다면 어떻게 해야 할까요?",
-      "result_a": "로그인 화면의 비밀번호 찾기 기능을 클릭하신 후, 안내에 따라 휴대폰 번호를 입력하시면 됩니다.",
-      "result_b": "인증번호를 받으신 후, 새로운 비밀번호를 설정하시면 됩니다."
-    },
-    {
-      "scenario": "회원님께서 비밀번호를 잊어버리셨고, 휴대폰 번호가 등록되어 있지 않은 경우에는 어떻게 해야 할까요?",
-      "result_c": "다른 본인확인 수단(예: 신용카드, 아이핀)을 이용하거나, 고객센터에 문의하셔서 도움을 받으실 수 있습니다."
-    }
-  ],
-  "cautions": [
-    "본인 확인 절차에 필요한 정보를 정확하게 입력해주시기 바랍니다.",
-    "비밀번호를 재설정하신 후에는 안전한 비밀번호를 설정하시고, 주기적으로 변경하는 것을 권장합니다."
-  ]
-}</t>
-  </si>
-  <si>
-    <t>{
-  "basic_rules": [
-    "주간 근무 시간이 40시간을 초과하는 경우 연장 수당이 발생합니다.",
-    "하루 8시간을 초과하여 근무하는 경우에도 연장 수당이 발생합니다."
-  ],
-  "examples": [
-    {
-      "scenario": "월요일부터 토요일까지 매일 8시간씩 총 48시간 근무하셨다면, 40시간을 초과한 8시간에 대해 연장 수당이 지급됩니다. 이 경우 주휴수당도 함께 지급될 수 있습니다. 주휴수당은 일주일에 15시간 이상 근무하신 경우에 발생하며, 근로기준법에 따라 지급 여부와 금액이 정해집니다.",
-      "result_a": "40시간 초과 근무에 대한 연장 수당 지급",
-      "result_b": "주휴수당 지급 여부 확인 및 지급 (15시간 이상 근무 시)"
-    },
-    {
-      "scenario": "월요일부터 금요일까지는 하루 8시간씩 근무하시고, 토요일에 4시간 근무하셨다면, 총 근무시간은 44시간입니다. 이 경우 4시간에 대한 연장 수당이 지급됩니다.",
-      "result_c": "4시간 초과 근무에 대한 연장 수당 지급"
-    }
-  ],
-  "cautions": [
-    "연장 근무에 대한 수당 지급 기준은 회사 내규 및 근로계약서에 따라 다를 수 있습니다. 따라서, 자세한 내용은 회사에 문의하시는 것이 좋습니다.",
-    "연장 근무 시간에 대한 정확한 기록을 유지하시는 것이 중요합니다."
-  ]
-}</t>
-  </si>
-  <si>
-    <t>{
-  "basic_rules": [
-    "근로자분께서 계약서에 명시된 소정근로일을 모두 근무하셨어야 합니다.",
-    "해당 주의 모든 계약 근무일에 대한 근무가 완료되어야 합니다. 즉, 소정근로일만 근무했다고 해서 주휴수당이 발생하는 것이 아니라, 계약된 모든 근무일에 대한 근무가 완료되어야 합니다."
-  ],
-  "examples": [
-    {
-      "scenario": "월요일부터 금요일까지가 소정근로일인 두 명의 근로자 A씨와 B씨가 있습니다. A씨는 월요일부터 금요일까지 5일 계약을, B씨는 월요일부터 일요일까지 7일 계약을 체결하였습니다. 두 분 모두 월요일부터 금요일까지 5일을 근무하셨습니다.",
-      "result_a": "A씨는 계약상 5일 근무만으로, 7일 계약이 아닌 경우이므로 주휴수당이 발생하지 않습니다.",
-      "result_b": "B씨는 계약상 7일 근무 중 5일을 근무하였지만, 나머지 2일은 휴무로 계약되어 있으므로 주휴수당이 발생합니다."
-    },
-    {
-      "scenario": "C씨는 토요일과 일요일이 포함된 7일 계약을 맺고 월요일부터 일요일까지 모두 근무하였습니다.  소정근로일은 월요일부터 금요일까지입니다.",
-      "result_c": "C씨는 소정근로일인 월요일부터 금요일까지 모두 근무하였고, 계약상 모든 근무일에 대한 근무를 완료하였으므로 주휴수당이 발생합니다."
-    }
-  ],
-  "cautions": [
-    "계약서에 명시된 소정근로일과 실제 근무일, 그리고 계약 기간을 정확히 확인하셔야 주휴수당 발생 여부를 판단할 수 있습니다.",
-    "회사 내부 규정이나 노동법에 따라 주휴수당 지급 기준이 다를 수 있으므로, 해당 내용을 꼼꼼하게 확인하시는 것이 좋습니다."
-  ]
-}</t>
-  </si>
-  <si>
-    <t>{
-  "basic_rules": [
-    "휴일수당은 사용자와 근로자 간의 계약서에 명시된 휴일, 그리고 법적으로 정해진 공휴일(임시공휴일 및 대체공휴일 포함)과 근로자의 날에 근무하신 경우 발생합니다.",
-    "휴일수당은 일반적으로 해당 근무일에 대한 기본 시급 또는 일급에 50%의 가산금이 더해져 지급됩니다."
-  ],
-  "examples": [
-    {
-      "scenario": "근로자 A씨가 5월 1일(근로자의 날)에 8시간 근무하였고, 시급이 10,000원이라고 가정해 보겠습니다.  같은 날 근로자 B씨도 4시간 근무하였습니다.",
-      "result_a": "A씨의 휴일수당은 (10,000원 × 8시간 × 1.5) = 120,000원 입니다.",
-      "result_b": "B씨의 휴일수당은 (10,000원 × 4시간 × 1.5) = 60,000원 입니다."
-    },
-    {
-      "scenario": "근로자 C씨가 설날(공휴일)에 6시간 근무하고, 일급이 80,000원이라고 가정해 보겠습니다.",
-      "result_c": "C씨의 휴일수당은 (80,000원 × 1.5) = 120,000원 입니다. 단, 계약에 다른 내용이 명시되어 있을 수 있으므로, 반드시 계약 내용을 확인하시기 바랍니다."
-    }
-  ],
-  "cautions": [
-    "계약서에 명시된 휴일 및 수당 지급 기준을 꼼꼼히 확인하시기 바랍니다.  계약 내용에 따라 휴일수당 지급 방식이 다를 수 있습니다.",
-    "회사 내규 및 관련 법률을 준수하여 휴일수당이 정확하게 지급되도록 주의하시기 바랍니다.  궁금한 사항은 담당자에게 문의해주세요."
-  ]
-}</t>
-  </si>
-  <si>
-    <t>{
-  "basic_rules": [
-    "노무비 명세서는 직접 입력하실 수 없으며, 시스템을 통해 자동으로 계산됩니다.",
-    "일용근로자계약서를 작성하고 근로자의 출퇴근 내역을 입력하시면 시스템에서 노무비 명세서를 자동으로 생성합니다."
-  ],
-  "examples": [
-    {
-      "scenario": "일용직 근로자 A씨가 10일간 근무하였고, 계약 시 임금은 일급 10만원으로 협의되었습니다.  주중 8일, 주말 2일 근무하였으며, 야간 근무는 없었습니다.  연장 근무는 하지 않았습니다.",
-      "result_a": "시스템은 계약서 상의 일급 10만원을 기준으로 기본 수당 80만원(10만원/일 * 8일)을 계산합니다.",
-      "result_b": "주말 근무에 대한 주휴수당은 별도로 계산되어 기본수당에 추가됩니다.  (주휴수당 계산 방식은 회사 내규에 따라 다를 수 있습니다.)"
-    },
-    {
-      "scenario": "일용직 근로자 B씨가 5일간 근무하였고, 일급 15만원으로 계약되었습니다.  주중 5일 근무하였고, 야간 근무와 연장 근무는 없었습니다.  다만, B씨는 회사 내규에 따라 주휴수당을 지급받지 않습니다.",
-      "result_c": "시스템은 계약서 상의 일급 15만원을 기준으로 기본 수당 75만원(15만원/일 * 5일)을 계산하며, 주휴수당은 지급되지 않습니다."
-    }
-  ],
-  "cautions": [
-    "노무비 명세서 금액 수정이 필요한 경우, 반드시 사유를 입력해주세요.  입력하신 사유는 추후 소명 자료로 활용됩니다.",
-    "시스템에서 자동으로 계산된 노무비 명세서 내용을 꼼꼼히 확인하시고, 잘못된 부분이 있다면 담당자에게 문의해주세요."
-  ]
-}</t>
-  </si>
-  <si>
-    <t>{
-  "basic_rules": [
-    "권한관리 &gt; 사업연결/등록신청 메뉴에서 사업을 검색하신 후, 원하시는 사업명 앞의 체크박스를 체크하시면 됩니다.",
-    "체크 후 사업연결 신청 버튼을 클릭하시면 사업 연결 신청이 완료됩니다."
-  ],
-  "examples": [
-    {
-      "scenario": "시공사 담당자께서 발주처 사업을 검색했으나, 해당 사업이 검색되지 않는 경우",
-      "result_a": "사업명을 정확하게 입력하셨는지 다시 한번 확인해주세요. 사업명이 유사한 경우가 많으므로 정확한 사업명을 입력하셔야 검색이 가능합니다.",
-      "result_b": "조달청을 통해 공기 연장이 이루어진 후 OnePMIS에서 공기 연장 처리가 되지 않아 사업 상태가 종료된 경우일 수 있습니다. 이 경우 사업명 왼쪽의 상태를 '전체' 또는 '완료'로 변경하여 검색해 보시기 바랍니다. 발주처 담당자께서는 사업 연결 후 공기 연장 처리를 꼭 해주셔야 합니다."
-    },
-    {
-      "scenario": "발주처 담당자가 사업 연결 후 공기 연장 처리를 하지 않은 경우",
-      "result_c": "추후 사업 진행에 차질이 발생할 수 있으므로, 발주처 담당자께서는 사업 연결 후 반드시 OnePMIS에서 공기 연장 처리를 완료해 주시기 바랍니다."
-    }
-  ],
-  "cautions": [
-    "시공사 및 건설사업관리자는 발주처가 사업에 연결되어 있지 않으면 사업 연결 신청을 할 수 없습니다. 발주처 담당자께서는 본인이 담당하는 사업에 항상 연결되어 있는지 확인해 주시기 바랍니다.",
-    "사업 검색 시 사업명을 정확하게 입력하지 않으면 검색 결과가 나타나지 않을 수 있습니다.  정확한 사업명을 입력하시는 것을 권장합니다."
-  ]
-}</t>
-  </si>
-  <si>
-    <t>[
-  "비밀번호",
-  "비밀번호찾기",
-  "로그인",
-  "본인확인",
-  "휴대폰",
-  "신용카드",
-  "아이핀",
-  "비밀번호 재설정",
-  "계정",
-  "보안",
-  "인증",
-  "분실",
-  "잊어버림",
-  "비밀 번호",
-  "본인 확인",
-  "휴대폰번호",
-  "신용 카드",
-  "아이 핀"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "연장수당",
-  "연장근무",
-  "초과근무",
-  "근로시간",
-  "주휴수당",
-  "주휴 수당",
-  "일꾼",
-  "근로자",
-  "휴일",
-  "쉬는 날",
-  "퇴직금",
-  "퇴직금여",
-  "시간외근무",
-  "40시간"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "주휴수당",
-  "주휴 수당",
-  "휴일수당",
-  "소정근로일",
-  "근로자",
-  "일꾼",
-  "개근",
-  "계약",
-  "근무",
-  "휴일",
-  "쉬는 날",
-  "주휴",
-  "소정",
-  "일주일"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "휴일수당",
-  "휴일",
-  "쉬는날",
-  "공휴일",
-  "근로자의날",
-  "근로자",
-  "일꾼",
-  "주휴수당",
-  "주휴 수당",
-  "수당",
-  "가산금",
-  "퇴직금",
-  "퇴직금여"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "노무비명세서",
-  "노무비 명세서",
-  "일용근로자",
-  "일꾼",
-  "계약서",
-  "출퇴근",
-  "근무시간",
-  "기본수당",
-  "연장수당",
-  "야간수당",
-  "휴일수당",
-  "쉬는날",
-  "주휴수당",
-  "주휴 수당",
-  "연차수당",
-  "소득세",
-  "원천징수",
-  "퇴직금",
-  "퇴직금여"
-]</t>
-  </si>
-  <si>
-    <t>[
-  "사업연결",
-  "사업 연결",
-  "권한관리",
-  "등록신청",
-  "공기연장",
-  "공기 연장",
-  "OnePMIS",
-  "발주처",
-  "시공사",
-  "건설사업관리자",
-  "사업명",
-  "체크박스",
-  "준공예정일",
-  "사업상태",
-  "종료"
-]</t>
+    <t>["비밀번호를 잊어버렸을 경우 어떻게 해야 하나요?", "혹시 비밀번호를 분실했을 때 어떤 절차를 거쳐야 하나요?", "로그인 비밀번호를 찾는 방법을 알려주시겠습니까?"]</t>
+  </si>
+  <si>
+    <t>["연장 근무 수당은 어떤 경우에 발생하나요?", "연장 수당은 어떠한 조건을 충족해야 지급되나요?", "연장근무에 대한 수당은 언제부터 발생하는 건가요?"]</t>
+  </si>
+  <si>
+    <t>["주휴수당이 발생하는 조건은 무엇인가요?", "주휴수당을 받으려면 어떤 요건을 충족해야 하나요?", "주휴수당 지급 조건에 대해 자세히 알고 싶습니다."]</t>
+  </si>
+  <si>
+    <t>["휴일 근무에 대한 수당은 어떻게 지급되나요?", "휴일 근무 시 추가로 받는 수당은 무엇인가요?", "공휴일에 일을 하면 어떤 수당을 받을 수 있나요?"]</t>
+  </si>
+  <si>
+    <t>["노무비명세서 작성 방법을 알려주시겠습니까?", "노무비명세서는 어떻게 작성해야 하나요?", "노무비명세서 작성 절차에 대해 자세히 설명해주시면 감사하겠습니다."]</t>
+  </si>
+  <si>
+    <t>["사업 연결 방법을 알려주시겠습니까?", "사업을 어떻게 연결할 수 있을까요?", "사업 연결 절차에 대해 자세히 안내해 주시면 감사하겠습니다."]</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["로그인 화면에서 '비밀번호 찾기' 또는 유사한 기능을 찾으세요.", "본인 확인 절차를 거쳐야 비밀번호를 찾을 수 있습니다. 일반적으로 휴대전화 번호, 신용카드 정보, 또는 아이핀 등을 이용한 본인 인증이 필요합니다."], "examples": [{"scenario": "회원님께서 이메일 주소와 휴대전화 번호를 모두 기억하시는 경우, 비밀번호 찾기 기능을 통해 본인 인증을 진행하시면 새로운 비밀번호를 설정하실 수 있습니다.", "result_a": "휴대전화 번호를 이용한 본인 인증이 성공적으로 완료되면, 새로운 비밀번호를 설정하는 화면으로 이동합니다.", "result_b": "이메일 주소를 통해서도 본인 인증이 가능하며, 인증 후 새로운 비밀번호를 설정하실 수 있습니다."}, {"scenario": "회원님께서 휴대전화 번호를 분실하셨거나 변경하신 경우, 신분증과 같은 추가적인 본인 확인 절차가 필요할 수 있습니다. 고객센터에 문의하시면 자세한 안내를 받으실 수 있습니다.", "result_c": "고객센터 상담원의 안내에 따라 추가적인 본인 확인 절차를 거치신 후, 비밀번호 재설정을 진행하실 수 있습니다."}], "cautions": ["비밀번호를 재설정하실 때는 안전하고 기억하기 쉬운 비밀번호를 설정하시는 것이 좋습니다.  다른 계정과 비밀번호를 중복해서 사용하지 않도록 주의해주세요.", "비밀번호 재설정 링크를 함부로 클릭하지 마시고, 출처를 꼼꼼히 확인하시기 바랍니다. 피싱 사이트에 의한 개인정보 유출의 위험이 있으므로 각별히 주의해주세요."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["주간 근무시간 40시간을 초과하였을 경우 연장 수당이 발생합니다.", "일일 근무시간 8시간을 초과하였을 경우 연장 수당이 발생합니다."], "examples": [{"scenario": "월요일부터 토요일까지 매일 8시간씩 총 48시간 근무하셨다면,", "result_a": "주간 근무시간 40시간을 초과한 8시간에 대해 연장 수당이 지급됩니다.", "result_b": "일일 근무시간 8시간을 초과한 시간은 없으므로, 토요일 근무시간 8시간에 대한 연장 수당만 지급됩니다."}, {"scenario": "월요일부터 금요일까지는 하루 8시간 근무하시고, 토요일에 4시간, 일요일에 2시간 추가 근무하셨다면,", "result_c": "토요일 4시간과 일요일 2시간, 총 6시간에 대한 연장 수당이 지급됩니다."}], "cautions": ["연장근무 시간 계산은 회사 내부 규정에 따라 다를 수 있으므로, 해당 규정을 확인하시는 것이 좋습니다.", "연장 수당 지급 기준 및 계산 방법에 대해서는 회사 인사부서에 문의하시는 것이 정확합니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["계약서 상에 명시된 소정 근로일을 모두 근무하셔야 합니다.", "해당 주의 모든 계약일에 대한 근무가 완료되어야 합니다."], "examples": [{"scenario": "월요일부터 금요일까지 근무하는 두 명의 근로자 A와 B가 있습니다. A는 월요일부터 금요일까지 5일 계약을 맺었고, B는 월요일부터 일요일까지 7일 계약을 맺었습니다. 두 근로자 모두 월요일부터 금요일까지 5일간 근무하였습니다.", "result_a": "A씨는 주휴수당이 발생하지 않습니다. 계약 기간이 해당 주의 모든 요일에 적용되지 않기 때문입니다.", "result_b": "B씨는 주휴수당이 발생합니다. 계약 기간이 해당 주의 모든 요일에 적용되기 때문입니다."}, {"scenario": "C씨는 토요일과 일요일을 제외한 월요일부터 금요일까지 근무하는 계약을 맺었습니다. 하지만 월요일부터 금요일까지 모두 근무하였습니다.", "result_c": "C씨는 주휴수당이 발생하지 않습니다. 계약상 주말 근무가 없으므로 해당 주의 모든 요일에 대한 근무가 완료되지 않았기 때문입니다."}], "cautions": ["계약서에 명시된 내용을 꼼꼼히 확인하시는 것이 중요합니다.", "회사 내부 규정 및 관련 법률을 충분히 이해하시는 것이 좋습니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["계약서에 명시된 휴일, 공휴일(임시공휴일 및 대체공휴일 포함), 근로자의 날에 근무하신 경우 휴일수당이 발생합니다.", "휴일수당은 기본 시급 또는 일급의 50%를 가산하여 지급됩니다."], "examples": [{"scenario": "회사와의 근로계약서에 토요일을 휴일로 명시하고, 해당 토요일에 근무하신 경우를 예로 들겠습니다. 또한, 5월 1일 근로자의 날에 근무하셨다고 가정하겠습니다.", "result_a": "토요일 근무에 대한 휴일수당이 발생하며, 기본급의 50%가 추가 지급됩니다.", "result_b": "근로자의 날 근무에 대한 휴일수당 또한 발생하며, 마찬가지로 기본급의 50%가 추가 지급됩니다."}, {"scenario": "설날(공휴일)에 근무하신 경우를 예로 들겠습니다.", "result_c": "설날 근무에 대한 휴일수당이 발생하며, 기본급의 50%가 추가 지급됩니다."}], "cautions": ["휴일수당 지급 기준은 회사 내규 및 근로계약서에 따라 상이할 수 있으므로, 자세한 내용은 해당 내용을 확인하시는 것이 좋습니다.", "휴일근무에 대한 수당 지급과 관련하여 궁금한 점이 있으시다면, 담당자에게 문의해주시기 바랍니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["노무비명세서는 직접 입력하실 수 없으며, 시스템을 통해 자동으로 계산됩니다.", "일용근로자계약서관리 메뉴에서 계약서를 작성하고, 출퇴근관리 메뉴에서 근무 내역을 입력하셔야 합니다."], "examples": [{"scenario": "계약서에 시급 10,000원으로 명시하고, 주 40시간 근무 후 주휴일 8시간을 포함하여 총 48시간 근무하였을 경우, 주휴수당을 포함한 노무비를 계산해주세요.  소득세 및 기타 공제는 고려하지 않습니다.", "result_a": "기본급은 40시간 * 10,000원/시간 = 400,000원 입니다.", "result_b": "주휴수당은 8시간 * 10,000원/시간 = 80,000원이며, 총 노무비는 480,000원이 됩니다."}, {"scenario": "근무 시간이 주 40시간을 초과하거나 야간, 휴일 근무가 있었을 경우, 연장, 야간, 휴일 수당이 추가로 계산됩니다.  계약서에 명시된 각 수당의 계산 방식에 따라 노무비가 산정됩니다.", "result_c": "시스템에서 계약서 내용과 근무 시간을 바탕으로 연장, 야간, 휴일 수당을 자동으로 계산하여 총 노무비에 반영합니다.  상세 내역은 노무비명세서에서 확인하실 수 있습니다."}], "cautions": ["노무비명세서 금액 수정 시에는 반드시 수정 사유를 입력해주셔야 합니다.  수정 사유는 추후 소명 자료로 사용됩니다.", "노무비명세서 작성 및 수정 과정에서 궁금한 점이 있으시면 언제든지 문의해주세요."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["권한관리 &gt; 사업연결/등록신청 메뉴를 통해 사업 연결 신청을 진행하실 수 있습니다.", "사업 검색 후, 사업명 앞의 체크박스를 선택하고 사업연결 신청 버튼을 클릭하여 신청을 완료하시면 됩니다."], "examples": [{"scenario": "시공사 담당자께서 발주처 사업에 연결을 원하시는 경우, 정확한 사업명을 입력하였음에도 검색이 되지 않는 상황입니다.", "result_a": "사업명 입력의 정확성을 다시 한번 확인해주시기 바랍니다. 사업명이 유사한 경우가 많으므로 정확한 명칭을 입력하셔야 검색이 가능합니다.", "result_b": "만약 조달청을 통해 공기 연장이 이루어진 후 OnePMIS에서 공기 연장 처리가 되지 않아 준공 예정일이 지난 경우, 사업 상태가 종료로 변경될 수 있습니다. 이 경우 사업명 왼쪽의 상태를 '전체' 또는 '완료'로 변경하여 검색해 보시기 바랍니다. 발주처 담당자께서는 사업 연결 후 공기 연장 처리를 반드시 완료해 주셔야 합니다."}, {"scenario": "건설사업관리자 담당자께서 사업 연결을 시도하였으나, 발주처가 해당 사업에 연결되어 있지 않아 연결 신청이 불가능한 상황입니다.", "result_c": "발주처 담당자께서 본인의 담당 사업에 연결되어 있는지 확인하시고, 연결이 되어있지 않다면 먼저 사업 연결을 진행하신 후 다시 시도해 주시기 바랍니다."}], "cautions": ["사업명 검색 시, 정확한 사업명을 입력하시는 것이 중요합니다. 유사한 사업명이 많으므로 주의해주세요.", "조달청 공기 연장 후 OnePMIS에서 공기 연장 처리를 하지 않으면 사업 상태가 종료되어 연결이 불가능할 수 있습니다.  발주처 담당자분들께서는 공기 연장 처리를 꼭 해주시기 바랍니다."]}</t>
+  </si>
+  <si>
+    <t>["비밀번호", "비밀번호 찾기", "로그인", "본인확인", "휴대폰", "신용카드", "아이핀", "본인인증", "계정", "비밀번호 재설정", "비밀 번호", "비밀번호찾기", "휴대 전화", "신용 카드", "개인정보", "피싱", "보안"]</t>
+  </si>
+  <si>
+    <t>["연장수당", "연장근무", "초과근무", "근무시간", "일꾼", "근로자", "주휴수당", "주휴 수당", "휴일수당", "쉬는날", "휴일", "퇴직금", "퇴직금여"]</t>
+  </si>
+  <si>
+    <t>["주휴수당", "주휴 수당", "주휴일", "쉬는 날", "근로자", "일꾼", "소정근로일", "계약일", "휴일수당", "개근", "근무", "퇴직금", "퇴직금여"]</t>
+  </si>
+  <si>
+    <t>["휴일수당", "휴일", "쉬는날", "공휴일", "근로자의날", "주휴수당", "주휴 수당", "근로자", "일꾼", "수당", "가산", "계약서", "임시공휴일", "대체공휴일", "휴일근무"]</t>
+  </si>
+  <si>
+    <t>["노무비명세서", "노무비 명세서", "임금", "급여", "근로자", "일꾼", "계약서", "근무시간", "출퇴근", "주휴수당", "주휴 수당", "휴일수당", "휴일 수당", "쉬는날", "연장수당", "연장 수당", "야간수당", "야간 수당", "연차수당", "연차 수당", "소득세", "원천징수", "퇴직금", "퇴직금여"]</t>
+  </si>
+  <si>
+    <t>["사업연결", "사업 연결", "권한관리", "등록신청", "공기연장", "공기 연장", "준공예정일", "준공 예정일", "OnePMIS", "발주처", "시공사", "건설사업관리자", "사업명", "체크박스", "상태", "전체", "완료", "조달청"]</t>
   </si>
 </sst>
 </file>

--- a/docs/enhanced_qa_pairs.xlsx
+++ b/docs/enhanced_qa_pairs.xlsx
@@ -46,58 +46,58 @@
     <t>사업연결은 어떻게해?</t>
   </si>
   <si>
-    <t>["비밀번호를 잊어버렸을 경우 어떻게 해야 하나요?", "혹시 비밀번호를 분실했을 때 어떤 절차를 거쳐야 하나요?", "로그인 비밀번호를 찾는 방법을 알려주시겠습니까?"]</t>
-  </si>
-  <si>
-    <t>["연장 근무 수당은 어떤 경우에 발생하나요?", "연장 수당은 어떠한 조건을 충족해야 지급되나요?", "연장근무에 대한 수당은 언제부터 발생하는 건가요?"]</t>
-  </si>
-  <si>
-    <t>["주휴수당이 발생하는 조건은 무엇인가요?", "주휴수당을 받으려면 어떤 요건을 충족해야 하나요?", "주휴수당 지급 조건에 대해 자세히 알고 싶습니다."]</t>
-  </si>
-  <si>
-    <t>["휴일 근무에 대한 수당은 어떻게 지급되나요?", "휴일 근무 시 추가로 받는 수당은 무엇인가요?", "공휴일에 일을 하면 어떤 수당을 받을 수 있나요?"]</t>
-  </si>
-  <si>
-    <t>["노무비명세서 작성 방법을 알려주시겠습니까?", "노무비명세서는 어떻게 작성해야 하나요?", "노무비명세서 작성 절차에 대해 자세히 설명해주시면 감사하겠습니다."]</t>
-  </si>
-  <si>
-    <t>["사업 연결 방법을 알려주시겠습니까?", "사업을 어떻게 연결할 수 있을까요?", "사업 연결 절차에 대해 자세히 안내해 주시면 감사하겠습니다."]</t>
-  </si>
-  <si>
-    <t>{"basic_rules": ["로그인 화면에서 '비밀번호 찾기' 또는 유사한 기능을 찾으세요.", "본인 확인 절차를 거쳐야 비밀번호를 찾을 수 있습니다. 일반적으로 휴대전화 번호, 신용카드 정보, 또는 아이핀 등을 이용한 본인 인증이 필요합니다."], "examples": [{"scenario": "회원님께서 이메일 주소와 휴대전화 번호를 모두 기억하시는 경우, 비밀번호 찾기 기능을 통해 본인 인증을 진행하시면 새로운 비밀번호를 설정하실 수 있습니다.", "result_a": "휴대전화 번호를 이용한 본인 인증이 성공적으로 완료되면, 새로운 비밀번호를 설정하는 화면으로 이동합니다.", "result_b": "이메일 주소를 통해서도 본인 인증이 가능하며, 인증 후 새로운 비밀번호를 설정하실 수 있습니다."}, {"scenario": "회원님께서 휴대전화 번호를 분실하셨거나 변경하신 경우, 신분증과 같은 추가적인 본인 확인 절차가 필요할 수 있습니다. 고객센터에 문의하시면 자세한 안내를 받으실 수 있습니다.", "result_c": "고객센터 상담원의 안내에 따라 추가적인 본인 확인 절차를 거치신 후, 비밀번호 재설정을 진행하실 수 있습니다."}], "cautions": ["비밀번호를 재설정하실 때는 안전하고 기억하기 쉬운 비밀번호를 설정하시는 것이 좋습니다.  다른 계정과 비밀번호를 중복해서 사용하지 않도록 주의해주세요.", "비밀번호 재설정 링크를 함부로 클릭하지 마시고, 출처를 꼼꼼히 확인하시기 바랍니다. 피싱 사이트에 의한 개인정보 유출의 위험이 있으므로 각별히 주의해주세요."]}</t>
-  </si>
-  <si>
-    <t>{"basic_rules": ["주간 근무시간 40시간을 초과하였을 경우 연장 수당이 발생합니다.", "일일 근무시간 8시간을 초과하였을 경우 연장 수당이 발생합니다."], "examples": [{"scenario": "월요일부터 토요일까지 매일 8시간씩 총 48시간 근무하셨다면,", "result_a": "주간 근무시간 40시간을 초과한 8시간에 대해 연장 수당이 지급됩니다.", "result_b": "일일 근무시간 8시간을 초과한 시간은 없으므로, 토요일 근무시간 8시간에 대한 연장 수당만 지급됩니다."}, {"scenario": "월요일부터 금요일까지는 하루 8시간 근무하시고, 토요일에 4시간, 일요일에 2시간 추가 근무하셨다면,", "result_c": "토요일 4시간과 일요일 2시간, 총 6시간에 대한 연장 수당이 지급됩니다."}], "cautions": ["연장근무 시간 계산은 회사 내부 규정에 따라 다를 수 있으므로, 해당 규정을 확인하시는 것이 좋습니다.", "연장 수당 지급 기준 및 계산 방법에 대해서는 회사 인사부서에 문의하시는 것이 정확합니다."]}</t>
-  </si>
-  <si>
-    <t>{"basic_rules": ["계약서 상에 명시된 소정 근로일을 모두 근무하셔야 합니다.", "해당 주의 모든 계약일에 대한 근무가 완료되어야 합니다."], "examples": [{"scenario": "월요일부터 금요일까지 근무하는 두 명의 근로자 A와 B가 있습니다. A는 월요일부터 금요일까지 5일 계약을 맺었고, B는 월요일부터 일요일까지 7일 계약을 맺었습니다. 두 근로자 모두 월요일부터 금요일까지 5일간 근무하였습니다.", "result_a": "A씨는 주휴수당이 발생하지 않습니다. 계약 기간이 해당 주의 모든 요일에 적용되지 않기 때문입니다.", "result_b": "B씨는 주휴수당이 발생합니다. 계약 기간이 해당 주의 모든 요일에 적용되기 때문입니다."}, {"scenario": "C씨는 토요일과 일요일을 제외한 월요일부터 금요일까지 근무하는 계약을 맺었습니다. 하지만 월요일부터 금요일까지 모두 근무하였습니다.", "result_c": "C씨는 주휴수당이 발생하지 않습니다. 계약상 주말 근무가 없으므로 해당 주의 모든 요일에 대한 근무가 완료되지 않았기 때문입니다."}], "cautions": ["계약서에 명시된 내용을 꼼꼼히 확인하시는 것이 중요합니다.", "회사 내부 규정 및 관련 법률을 충분히 이해하시는 것이 좋습니다."]}</t>
-  </si>
-  <si>
-    <t>{"basic_rules": ["계약서에 명시된 휴일, 공휴일(임시공휴일 및 대체공휴일 포함), 근로자의 날에 근무하신 경우 휴일수당이 발생합니다.", "휴일수당은 기본 시급 또는 일급의 50%를 가산하여 지급됩니다."], "examples": [{"scenario": "회사와의 근로계약서에 토요일을 휴일로 명시하고, 해당 토요일에 근무하신 경우를 예로 들겠습니다. 또한, 5월 1일 근로자의 날에 근무하셨다고 가정하겠습니다.", "result_a": "토요일 근무에 대한 휴일수당이 발생하며, 기본급의 50%가 추가 지급됩니다.", "result_b": "근로자의 날 근무에 대한 휴일수당 또한 발생하며, 마찬가지로 기본급의 50%가 추가 지급됩니다."}, {"scenario": "설날(공휴일)에 근무하신 경우를 예로 들겠습니다.", "result_c": "설날 근무에 대한 휴일수당이 발생하며, 기본급의 50%가 추가 지급됩니다."}], "cautions": ["휴일수당 지급 기준은 회사 내규 및 근로계약서에 따라 상이할 수 있으므로, 자세한 내용은 해당 내용을 확인하시는 것이 좋습니다.", "휴일근무에 대한 수당 지급과 관련하여 궁금한 점이 있으시다면, 담당자에게 문의해주시기 바랍니다."]}</t>
-  </si>
-  <si>
-    <t>{"basic_rules": ["노무비명세서는 직접 입력하실 수 없으며, 시스템을 통해 자동으로 계산됩니다.", "일용근로자계약서관리 메뉴에서 계약서를 작성하고, 출퇴근관리 메뉴에서 근무 내역을 입력하셔야 합니다."], "examples": [{"scenario": "계약서에 시급 10,000원으로 명시하고, 주 40시간 근무 후 주휴일 8시간을 포함하여 총 48시간 근무하였을 경우, 주휴수당을 포함한 노무비를 계산해주세요.  소득세 및 기타 공제는 고려하지 않습니다.", "result_a": "기본급은 40시간 * 10,000원/시간 = 400,000원 입니다.", "result_b": "주휴수당은 8시간 * 10,000원/시간 = 80,000원이며, 총 노무비는 480,000원이 됩니다."}, {"scenario": "근무 시간이 주 40시간을 초과하거나 야간, 휴일 근무가 있었을 경우, 연장, 야간, 휴일 수당이 추가로 계산됩니다.  계약서에 명시된 각 수당의 계산 방식에 따라 노무비가 산정됩니다.", "result_c": "시스템에서 계약서 내용과 근무 시간을 바탕으로 연장, 야간, 휴일 수당을 자동으로 계산하여 총 노무비에 반영합니다.  상세 내역은 노무비명세서에서 확인하실 수 있습니다."}], "cautions": ["노무비명세서 금액 수정 시에는 반드시 수정 사유를 입력해주셔야 합니다.  수정 사유는 추후 소명 자료로 사용됩니다.", "노무비명세서 작성 및 수정 과정에서 궁금한 점이 있으시면 언제든지 문의해주세요."]}</t>
-  </si>
-  <si>
-    <t>{"basic_rules": ["권한관리 &gt; 사업연결/등록신청 메뉴를 통해 사업 연결 신청을 진행하실 수 있습니다.", "사업 검색 후, 사업명 앞의 체크박스를 선택하고 사업연결 신청 버튼을 클릭하여 신청을 완료하시면 됩니다."], "examples": [{"scenario": "시공사 담당자께서 발주처 사업에 연결을 원하시는 경우, 정확한 사업명을 입력하였음에도 검색이 되지 않는 상황입니다.", "result_a": "사업명 입력의 정확성을 다시 한번 확인해주시기 바랍니다. 사업명이 유사한 경우가 많으므로 정확한 명칭을 입력하셔야 검색이 가능합니다.", "result_b": "만약 조달청을 통해 공기 연장이 이루어진 후 OnePMIS에서 공기 연장 처리가 되지 않아 준공 예정일이 지난 경우, 사업 상태가 종료로 변경될 수 있습니다. 이 경우 사업명 왼쪽의 상태를 '전체' 또는 '완료'로 변경하여 검색해 보시기 바랍니다. 발주처 담당자께서는 사업 연결 후 공기 연장 처리를 반드시 완료해 주셔야 합니다."}, {"scenario": "건설사업관리자 담당자께서 사업 연결을 시도하였으나, 발주처가 해당 사업에 연결되어 있지 않아 연결 신청이 불가능한 상황입니다.", "result_c": "발주처 담당자께서 본인의 담당 사업에 연결되어 있는지 확인하시고, 연결이 되어있지 않다면 먼저 사업 연결을 진행하신 후 다시 시도해 주시기 바랍니다."}], "cautions": ["사업명 검색 시, 정확한 사업명을 입력하시는 것이 중요합니다. 유사한 사업명이 많으므로 주의해주세요.", "조달청 공기 연장 후 OnePMIS에서 공기 연장 처리를 하지 않으면 사업 상태가 종료되어 연결이 불가능할 수 있습니다.  발주처 담당자분들께서는 공기 연장 처리를 꼭 해주시기 바랍니다."]}</t>
-  </si>
-  <si>
-    <t>["비밀번호", "비밀번호 찾기", "로그인", "본인확인", "휴대폰", "신용카드", "아이핀", "본인인증", "계정", "비밀번호 재설정", "비밀 번호", "비밀번호찾기", "휴대 전화", "신용 카드", "개인정보", "피싱", "보안"]</t>
-  </si>
-  <si>
-    <t>["연장수당", "연장근무", "초과근무", "근무시간", "일꾼", "근로자", "주휴수당", "주휴 수당", "휴일수당", "쉬는날", "휴일", "퇴직금", "퇴직금여"]</t>
-  </si>
-  <si>
-    <t>["주휴수당", "주휴 수당", "주휴일", "쉬는 날", "근로자", "일꾼", "소정근로일", "계약일", "휴일수당", "개근", "근무", "퇴직금", "퇴직금여"]</t>
-  </si>
-  <si>
-    <t>["휴일수당", "휴일", "쉬는날", "공휴일", "근로자의날", "주휴수당", "주휴 수당", "근로자", "일꾼", "수당", "가산", "계약서", "임시공휴일", "대체공휴일", "휴일근무"]</t>
-  </si>
-  <si>
-    <t>["노무비명세서", "노무비 명세서", "임금", "급여", "근로자", "일꾼", "계약서", "근무시간", "출퇴근", "주휴수당", "주휴 수당", "휴일수당", "휴일 수당", "쉬는날", "연장수당", "연장 수당", "야간수당", "야간 수당", "연차수당", "연차 수당", "소득세", "원천징수", "퇴직금", "퇴직금여"]</t>
-  </si>
-  <si>
-    <t>["사업연결", "사업 연결", "권한관리", "등록신청", "공기연장", "공기 연장", "준공예정일", "준공 예정일", "OnePMIS", "발주처", "시공사", "건설사업관리자", "사업명", "체크박스", "상태", "전체", "완료", "조달청"]</t>
+    <t>["혹시 비밀번호를 잊어버리면 어떻게 해야 하나요?", "비밀번호를 분실했는데, 어떻게 찾을 수 있을까요?", "로그인 비밀번호가 기억나지 않습니다. 어떤 방법으로 찾을 수 있을까요?"]</t>
+  </si>
+  <si>
+    <t>["연장수당은 어떤 경우에 지급받을 수 있나요?", "연장근무에 대한 수당은 어떻게 계산되나요?", "연장 근무 시 수당 발생 조건을 알려주세요."]</t>
+  </si>
+  <si>
+    <t>["주휴수당이 발생하는 조건에 대해 자세히 설명해주시겠습니까?", "주휴수당 지급과 관련된 조건은 무엇인가요?", "어떤 경우에 주휴수당을 받을 수 있을까요?"]</t>
+  </si>
+  <si>
+    <t>["휴일 근무 시 수당 지급 기준은 어떻게 되나요?", "휴일 근무에 대한 수당은 어떤 경우에 발생하나요?", "휴일 수당은 어떠한 상황에서 받을 수 있나요?"]</t>
+  </si>
+  <si>
+    <t>["노무비명세서 작성 방법을 알려주시겠습니까?", "노무비명세서는 어떻게 작성해야 하나요?", "노무비명세서를 작성하는 절차를 자세히 설명해주시면 감사하겠습니다."]</t>
+  </si>
+  <si>
+    <t>["사업 연결 방법을 알려주시겠습니까?", "사업을 어떻게 연결할 수 있을까요?", "사업 연결 절차에 대해 자세히 설명해 주시면 감사하겠습니다."]</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["로그인 화면에서 비밀번호 찾기 기능을 이용하시면 됩니다.", "본인 확인 절차를 거쳐야 비밀번호를 찾을 수 있습니다."], "examples": [{"scenario": "회원님께서 비밀번호를 잊어버리셔서 로그인이 되지 않는 상황입니다. 휴대전화 번호와 이메일 주소는 모두 기억나시는 상황입니다.", "result_a": "로그인 화면의 '비밀번호 찾기'를 클릭하신 후, 안내에 따라 휴대전화 번호 또는 이메일 주소를 입력하시면 됩니다.", "result_b": "본인 확인을 위한 인증 절차(SMS 인증 또는 이메일 인증)를 거치신 후, 새로운 비밀번호를 설정하실 수 있습니다."}, {"scenario": "회원님께서 비밀번호를 잊어버리셨고, 휴대전화 번호는 변경되어 기억나지 않지만, 신용카드 정보는 기억나시는 상황입니다.", "result_c": "로그인 화면의 '비밀번호 찾기'를 클릭하신 후, 안내에 따라 신용카드 정보를 입력하여 본인 확인을 진행하시면 비밀번호를 재설정하실 수 있습니다.  만약 신용카드 정보가 없다면, 다른 본인 확인 수단(예: 아이핀)을 이용하실 수 있습니다."}], "cautions": ["본인 확인 절차는 개인 정보 보호를 위해 매우 중요하므로, 정확한 정보를 입력해주시기 바랍니다.", "비밀번호를 재설정하신 후에는 안전한 비밀번호를 설정하고, 주기적으로 변경하는 것을 권장합니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["주간 근무 시간이 40시간을 초과하였을 경우 연장수당이 발생합니다.", "하루 8시간을 초과하여 근무하였을 경우 연장수당이 발생합니다."], "examples": [{"scenario": "월요일부터 토요일까지 매일 8시간씩 근무하셨다고 가정하면 총 48시간이 됩니다. 이 경우 40시간을 초과한 8시간에 대해 연장수당이 지급됩니다.", "result_a": "총 근무시간: 48시간", "result_b": "연장근무시간: 8시간 (48시간 - 40시간)"}, {"scenario": "어느 날 야근으로 인해 10시간 근무하셨다면, 8시간을 초과한 2시간에 대해 연장수당이 지급됩니다.", "result_c": "연장근무시간: 2시간 (10시간 - 8시간)"}], "cautions": ["연장수당 지급 기준 및 계산 방법은 회사 내규에 따라 다를 수 있으므로, 자세한 내용은 회사 인사부서에 문의하시는 것이 좋습니다.", "연장근무는 회사의 승인을 받아야 정상적으로 연장수당이 지급됩니다. 무단 연장근무는 연장수당 지급 대상이 아닐 수 있습니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["근로자분께서 계약서에 명시된 소정근로일을 모두 출근하셔야 합니다.", "해당 주의 모든 근무일에 대한 계약이 체결되어 있어야 합니다."], "examples": [{"scenario": "월요일부터 금요일까지 근무하는 두 명의 근로자 A, B가 있습니다. A씨는 월요일부터 금요일까지 5일 계약을 맺었고, B씨는 월요일부터 일요일까지 7일 계약을 맺었습니다.", "result_a": "A씨는 주중 5일만 계약되어 있으므로 주휴수당이 발생하지 않습니다.", "result_b": "B씨는 주 7일 계약되어 있으므로 주휴수당이 발생합니다."}, {"scenario": "C씨는 토요일에 추가 근무 계약을 맺고 소정근로일(월~금)을 모두 출근하였습니다.", "result_c": "C씨는 소정근로일을 모두 출근하였고, 주중 근무일에 대한 계약이 체결되어 있으므로 주휴수당이 발생합니다."}], "cautions": ["계약서에 명시된 소정근로일과 실제 근무일을 꼼꼼히 확인하시는 것이 중요합니다.", "주휴수당 발생 여부는 개별 근로계약 및 회사 내규에 따라 다를 수 있으므로, 해당 내용을 자세히 확인하시는 것이 좋습니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["계약서에 명시된 휴일, 공휴일(임시공휴일 및 대체공휴일 포함), 근로자의 날에 근무하신 경우 휴일수당이 발생합니다.", "휴일수당은 기본 시급 또는 일급의 50%를 가산하여 지급됩니다."], "examples": [{"scenario": "회사와의 계약서에 명시된 휴일인 토요일에 근무하셨고, 이에 대한 근무시간이 기록되어 있습니다. 또한, 이 날이 공휴일과 겹치지 않습니다.", "result_a": "해당 토요일 근무에 대해서는 기본 시급의 50%를 가산한 휴일수당이 지급됩니다.", "result_b": "기본 급여 외에 휴일 근무에 대한 추가 수당이 지급됩니다."}, {"scenario": "근로자의 날인 5월 1일에 근무하셨습니다.", "result_c": "근로자의 날 근무에 대해 기본 시급의 50%를 가산한 휴일수당이 지급됩니다."}], "cautions": ["휴일수당 지급 여부는 회사 내규 및 근로계약서에 명시된 내용을 기준으로 합니다.  계약서 내용을 꼼꼼히 확인하시는 것이 좋습니다.", "휴일 근무에 대한 수당 지급과 관련하여 궁금한 사항이 있으시면 담당자에게 문의해주시기 바랍니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["노무비명세서는 직접 입력하실 수 없으며, 시스템을 통해 자동 계산됩니다.", "일용근로자계약서를 작성하고 근로자의 출퇴근 내역을 입력해야 노무비가 계산됩니다."], "examples": [{"scenario": "일용근로자 A씨와 계약서를 작성하고, 주간 8시간, 야간 2시간 근무하였습니다. 주휴수당 적용 대상입니다.", "result_a": "시스템은 계약서 상의 임금과 근무 시간을 바탕으로 기본 수당, 야간 수당을 계산합니다.", "result_b": "주휴수당 또한 계산되어 노무비명세서에 포함됩니다."}, {"scenario": "일용근로자 B씨와 계약서를 작성하고, 주간 40시간 근무하였으며, 주휴수당 적용 대상이 아닙니다.", "result_c": "시스템은 계약서 상의 임금과 근무 시간을 바탕으로 기본 수당만 계산하고, 주휴수당은 포함되지 않습니다."}], "cautions": ["노무비명세서 금액을 수정하실 경우, 반드시 수정 사유를 입력해주셔야 합니다.", "수정 사유는 추후 금액 수정에 대한 소명 자료로 사용될 수 있습니다."]}</t>
+  </si>
+  <si>
+    <t>{"basic_rules": ["권한관리 &gt; 사업연결/등록신청 메뉴에서 사업 검색을 진행해 주세요.", "검색된 사업 목록에서 연결하고자 하는 사업명 앞의 체크박스를 체크하고, 사업연결 신청 버튼을 클릭하여 신청을 완료해 주세요."], "examples": [{"scenario": "시공사 담당자가 발주처 사업에 연결하고자 할 때, 정확한 사업명을 알고 있고 발주처 사업의 상태가 '전체' 또는 '완료' 상태인 경우", "result_a": "사업 검색 결과가 정상적으로 나타나며, 체크박스를 선택하고 사업연결 신청 버튼을 클릭하여 사업 연결을 진행할 수 있습니다.", "result_b": "사업 연결 신청이 성공적으로 완료되면, 해당 사업에 대한 정보를 확인하고 업무를 진행할 수 있습니다."}, {"scenario": "발주처 사업의 공기가 연장되었으나 OnePMIS에서 공기연장 처리가 되지 않아 사업 상태가 '종료'로 변경된 경우", "result_c": "사업 검색 시 해당 사업이 검색되지 않을 수 있습니다. 이 경우, 사업 상태를 '전체' 또는 '완료'로 변경하여 검색하면 해당 사업을 찾을 수 있으며, 사업 연결 후 발주처 담당자는 OnePMIS에서 공기 연장 처리를 반드시 해주셔야 합니다."}], "cautions": ["시공사 및 건설사업관리자는 발주처가 사업에 연결되어 있지 않으면 사업 연결 신청을 할 수 없습니다. 발주처는 담당 사업에 항상 연결되어 있는지 확인해 주세요.", "사업 검색이 되지 않는 경우, 사업명을 정확하게 입력했는지 확인하고, 사업 상태를 확인하여 '전체' 또는 '완료'로 변경 후 검색해 보세요."]}</t>
+  </si>
+  <si>
+    <t>["비밀번호", "비밀번호 찾기", "로그인", "본인확인", "휴대폰", "신용카드", "아이핀", "비밀번호 재설정", "계정", "인증", "비밀 번호", "본인 확인"]</t>
+  </si>
+  <si>
+    <t>["연장수당", "연장근무", "초과근무", "근로시간", "근무시간", "일꾼", "근로자", "주휴수당", "주휴 수당", "휴일수당", "휴일", "쉬는날", "퇴직금", "퇴직금여"]</t>
+  </si>
+  <si>
+    <t>["주휴수당", "주휴 수당", "소정근로일", "소정 근로일", "근로자", "일꾼", "계약", "개근", "휴일", "쉬는 날", "주휴일", "일주일", "휴일수당", "퇴직금", "퇴직금여"]</t>
+  </si>
+  <si>
+    <t>["휴일수당", "휴일", "쉬는날", "공휴일", "근로자의날", "근로자", "일꾼", "수당", "주휴수당", "주휴 수당", "임시공휴일", "대체공휴일", "계약서", "시급", "일급", "가산", "퇴직금", "퇴직금여"]</t>
+  </si>
+  <si>
+    <t>["노무비명세서", "노무비 명세서", "일용근로자", "일꾼", "계약서", "출퇴근", "근무시간", "기본수당", "연장수당", "야간수당", "휴일수당", "쉬는날", "주휴수당", "주휴 수당", "연차수당", "소득세", "원천징수", "임금", "수당", "퇴직금", "퇴직금여"]</t>
+  </si>
+  <si>
+    <t>["사업연결", "사업 연결", "권한관리", "등록신청", "공기연장", "공기 연장", "준공예정일", "사업명", "체크박스", "발주처", "시공사", "건설사업관리자", "OnePMIS", "상태", "전체", "완료", "종료"]</t>
   </si>
 </sst>
 </file>
